--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T09:28:26+00:00</t>
+    <t>2025-02-06T11:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T11:21:55+00:00</t>
+    <t>2025-02-06T12:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:00:33+00:00</t>
+    <t>2025-02-10T09:34:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T09:34:03+00:00</t>
+    <t>2025-02-10T11:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,19 +97,13 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>ValueSet URL</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActIncidentCode</t>
+  </si>
+  <si>
     <t>Concept</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Arbeitsunfall</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Schüler-/Studentenunfall</t>
   </si>
   <si>
     <t>3</t>
@@ -400,7 +395,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -411,48 +406,72 @@
       <c r="A1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -461,22 +480,6 @@
       </c>
       <c r="B7" t="s" s="2">
         <v>39</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-VerdachtArbeitsSchuelerunfall-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-VerdachtArbeitsSchuelerunfall-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -58,19 +58,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/ValueSet-moped-VerdachtArbeitsSchuelerunfall-valueset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
